--- a/TestData/TMTI0075758_75760_75767_75769_EventExpense_ApproveEventExpenseFormAsSecondLevelApprover.xlsx
+++ b/TestData/TMTI0075758_75760_75767_75769_EventExpense_ApproveEventExpenseFormAsSecondLevelApprover.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D166E37-48FC-4FBE-B24B-36372159D222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A94F6652-4B5A-4F40-85C4-E300B9394493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ExpenseRequest" sheetId="1" r:id="rId1"/>
@@ -168,7 +168,7 @@
     <t>klulla@hl.com.test</t>
   </si>
   <si>
-    <t>Bingo@123456</t>
+    <t>Bingo@12345</t>
   </si>
 </sst>
 </file>
@@ -925,9 +925,9 @@
     <hyperlink ref="A3" r:id="rId3" xr:uid="{9611F415-59B6-42E8-B992-4BDF4D2EA082}"/>
     <hyperlink ref="A4" r:id="rId4" tooltip="mailto:klulla@hl.com.test" display="mailto:klulla@hl.com.test" xr:uid="{37F6AA7D-E662-440D-B4E4-A870523B1294}"/>
     <hyperlink ref="A5" r:id="rId5" tooltip="mailto:klulla@hl.com.test" display="mailto:klulla@hl.com.test" xr:uid="{E27BE1ED-8298-4193-B17A-83CF275488FA}"/>
-    <hyperlink ref="B3" r:id="rId6" xr:uid="{38F38A15-5B0A-4127-AAED-85AAC31E8064}"/>
-    <hyperlink ref="B4" r:id="rId7" xr:uid="{8436A825-C06B-4179-968F-EB2AF3A77843}"/>
-    <hyperlink ref="B5" r:id="rId8" xr:uid="{328FF362-B60B-4301-A3C3-759546B5B692}"/>
+    <hyperlink ref="B3" r:id="rId6" xr:uid="{14605699-4141-4582-914A-A11AABC30370}"/>
+    <hyperlink ref="B4" r:id="rId7" xr:uid="{2A32E0A2-8519-48D0-8E95-97389F0BDDD3}"/>
+    <hyperlink ref="B5" r:id="rId8" xr:uid="{F51EEEFC-EDF4-40C8-B70C-EDDA46504948}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId9"/>
@@ -1000,9 +1000,9 @@
     <hyperlink ref="A3" r:id="rId1" xr:uid="{43CB4C96-EF8E-466C-A098-71C8B71DE9CE}"/>
     <hyperlink ref="A5" r:id="rId2" xr:uid="{F09A18C6-7321-4E0E-B9D9-D9B996CDFDA6}"/>
     <hyperlink ref="B2" r:id="rId3" xr:uid="{98E92ADE-69BD-431C-844E-19278F764E87}"/>
-    <hyperlink ref="B3" r:id="rId4" xr:uid="{CA1B6722-A2DE-49FA-A2CD-81F6BF2C4350}"/>
-    <hyperlink ref="B4" r:id="rId5" xr:uid="{B9C345D4-0330-4FF6-BE76-6AFC81FA6AC5}"/>
-    <hyperlink ref="B5" r:id="rId6" xr:uid="{43C2C13E-7293-4ADC-B6B5-8A818FEB2FFC}"/>
+    <hyperlink ref="B3" r:id="rId4" xr:uid="{EB72EFF0-83A0-443B-9185-430E2226C809}"/>
+    <hyperlink ref="B4" r:id="rId5" xr:uid="{D1EB8FFB-0865-4CE2-BE87-112443020732}"/>
+    <hyperlink ref="B5" r:id="rId6" xr:uid="{15A92461-D135-45E8-9987-E8BE39328FE5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId7"/>

--- a/TestData/TMTI0075758_75760_75767_75769_EventExpense_ApproveEventExpenseFormAsSecondLevelApprover.xlsx
+++ b/TestData/TMTI0075758_75760_75767_75769_EventExpense_ApproveEventExpenseFormAsSecondLevelApprover.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A94F6652-4B5A-4F40-85C4-E300B9394493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E047BFC6-5A1C-4377-A1F8-EBBEEBD39EC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ExpenseRequest" sheetId="1" r:id="rId1"/>
-    <sheet name="Users" sheetId="2" r:id="rId2"/>
-    <sheet name="FirstLevelApprover" sheetId="3" r:id="rId3"/>
-    <sheet name="Approver" sheetId="4" r:id="rId4"/>
+    <sheet name="Users" sheetId="2" r:id="rId1"/>
+    <sheet name="AppName" sheetId="5" r:id="rId2"/>
+    <sheet name="ModuleName" sheetId="6" r:id="rId3"/>
+    <sheet name="EventExp" sheetId="1" r:id="rId4"/>
+    <sheet name="FirstLevelApprover" sheetId="3" r:id="rId5"/>
+    <sheet name="Approver" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="51">
   <si>
     <t>LOB</t>
   </si>
@@ -96,9 +98,6 @@
     <t>Users</t>
   </si>
   <si>
-    <t>Sonika Goyal</t>
-  </si>
-  <si>
     <t>1-10</t>
   </si>
   <si>
@@ -169,6 +168,21 @@
   </si>
   <si>
     <t>Bingo@12345</t>
+  </si>
+  <si>
+    <t>Vijay Kumar</t>
+  </si>
+  <si>
+    <t>App Name</t>
+  </si>
+  <si>
+    <t>HL Banker</t>
+  </si>
+  <si>
+    <t>Module Name</t>
+  </si>
+  <si>
+    <t>Expense Request(LWC)</t>
   </si>
 </sst>
 </file>
@@ -506,27 +520,117 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46D7D1CC-B1D0-4F56-A587-6D120F49B0CC}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE98C5BF-4C2B-4F57-85F9-07C46652EE69}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -577,39 +681,39 @@
       </c>
       <c r="Q1" s="1"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" t="s">
         <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" t="s">
-        <v>25</v>
       </c>
       <c r="G2" t="s">
         <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>20</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>16</v>
@@ -618,110 +722,110 @@
         <v>17</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="Q2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R2">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" t="s">
         <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" t="s">
-        <v>25</v>
       </c>
       <c r="G3" t="s">
         <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="Q3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R3">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" t="s">
         <v>28</v>
       </c>
-      <c r="C4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="I4" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="H4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>16</v>
@@ -730,10 +834,10 @@
         <v>17</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>18</v>
@@ -745,51 +849,51 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
         <v>28</v>
       </c>
-      <c r="C5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="I5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="J5" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>17</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>18</v>
@@ -807,112 +911,62 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C2">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="C4">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="C5">
         <v>9</v>
@@ -934,62 +988,62 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>32</v>
-      </c>
       <c r="B2" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C2">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C4">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C5">
         <v>9</v>

--- a/TestData/TMTI0075758_75760_75767_75769_EventExpense_ApproveEventExpenseFormAsSecondLevelApprover.xlsx
+++ b/TestData/TMTI0075758_75760_75767_75769_EventExpense_ApproveEventExpenseFormAsSecondLevelApprover.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D166E37-48FC-4FBE-B24B-36372159D222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E047BFC6-5A1C-4377-A1F8-EBBEEBD39EC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ExpenseRequest" sheetId="1" r:id="rId1"/>
-    <sheet name="Users" sheetId="2" r:id="rId2"/>
-    <sheet name="FirstLevelApprover" sheetId="3" r:id="rId3"/>
-    <sheet name="Approver" sheetId="4" r:id="rId4"/>
+    <sheet name="Users" sheetId="2" r:id="rId1"/>
+    <sheet name="AppName" sheetId="5" r:id="rId2"/>
+    <sheet name="ModuleName" sheetId="6" r:id="rId3"/>
+    <sheet name="EventExp" sheetId="1" r:id="rId4"/>
+    <sheet name="FirstLevelApprover" sheetId="3" r:id="rId5"/>
+    <sheet name="Approver" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="51">
   <si>
     <t>LOB</t>
   </si>
@@ -96,9 +98,6 @@
     <t>Users</t>
   </si>
   <si>
-    <t>Sonika Goyal</t>
-  </si>
-  <si>
     <t>1-10</t>
   </si>
   <si>
@@ -168,7 +167,22 @@
     <t>klulla@hl.com.test</t>
   </si>
   <si>
-    <t>Bingo@123456</t>
+    <t>Bingo@12345</t>
+  </si>
+  <si>
+    <t>Vijay Kumar</t>
+  </si>
+  <si>
+    <t>App Name</t>
+  </si>
+  <si>
+    <t>HL Banker</t>
+  </si>
+  <si>
+    <t>Module Name</t>
+  </si>
+  <si>
+    <t>Expense Request(LWC)</t>
   </si>
 </sst>
 </file>
@@ -506,27 +520,117 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46D7D1CC-B1D0-4F56-A587-6D120F49B0CC}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE98C5BF-4C2B-4F57-85F9-07C46652EE69}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -577,39 +681,39 @@
       </c>
       <c r="Q1" s="1"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" t="s">
         <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" t="s">
-        <v>25</v>
       </c>
       <c r="G2" t="s">
         <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>20</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>16</v>
@@ -618,110 +722,110 @@
         <v>17</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="Q2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R2">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" t="s">
         <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" t="s">
-        <v>25</v>
       </c>
       <c r="G3" t="s">
         <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="Q3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R3">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" t="s">
         <v>28</v>
       </c>
-      <c r="C4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="I4" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="H4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>16</v>
@@ -730,10 +834,10 @@
         <v>17</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>18</v>
@@ -745,51 +849,51 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
         <v>28</v>
       </c>
-      <c r="C5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="I5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="J5" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>17</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>18</v>
@@ -807,112 +911,62 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C2">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="C4">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="C5">
         <v>9</v>
@@ -925,71 +979,71 @@
     <hyperlink ref="A3" r:id="rId3" xr:uid="{9611F415-59B6-42E8-B992-4BDF4D2EA082}"/>
     <hyperlink ref="A4" r:id="rId4" tooltip="mailto:klulla@hl.com.test" display="mailto:klulla@hl.com.test" xr:uid="{37F6AA7D-E662-440D-B4E4-A870523B1294}"/>
     <hyperlink ref="A5" r:id="rId5" tooltip="mailto:klulla@hl.com.test" display="mailto:klulla@hl.com.test" xr:uid="{E27BE1ED-8298-4193-B17A-83CF275488FA}"/>
-    <hyperlink ref="B3" r:id="rId6" xr:uid="{38F38A15-5B0A-4127-AAED-85AAC31E8064}"/>
-    <hyperlink ref="B4" r:id="rId7" xr:uid="{8436A825-C06B-4179-968F-EB2AF3A77843}"/>
-    <hyperlink ref="B5" r:id="rId8" xr:uid="{328FF362-B60B-4301-A3C3-759546B5B692}"/>
+    <hyperlink ref="B3" r:id="rId6" xr:uid="{14605699-4141-4582-914A-A11AABC30370}"/>
+    <hyperlink ref="B4" r:id="rId7" xr:uid="{2A32E0A2-8519-48D0-8E95-97389F0BDDD3}"/>
+    <hyperlink ref="B5" r:id="rId8" xr:uid="{F51EEEFC-EDF4-40C8-B70C-EDDA46504948}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId9"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>32</v>
-      </c>
       <c r="B2" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C2">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C4">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C5">
         <v>9</v>
@@ -1000,9 +1054,9 @@
     <hyperlink ref="A3" r:id="rId1" xr:uid="{43CB4C96-EF8E-466C-A098-71C8B71DE9CE}"/>
     <hyperlink ref="A5" r:id="rId2" xr:uid="{F09A18C6-7321-4E0E-B9D9-D9B996CDFDA6}"/>
     <hyperlink ref="B2" r:id="rId3" xr:uid="{98E92ADE-69BD-431C-844E-19278F764E87}"/>
-    <hyperlink ref="B3" r:id="rId4" xr:uid="{CA1B6722-A2DE-49FA-A2CD-81F6BF2C4350}"/>
-    <hyperlink ref="B4" r:id="rId5" xr:uid="{B9C345D4-0330-4FF6-BE76-6AFC81FA6AC5}"/>
-    <hyperlink ref="B5" r:id="rId6" xr:uid="{43C2C13E-7293-4ADC-B6B5-8A818FEB2FFC}"/>
+    <hyperlink ref="B3" r:id="rId4" xr:uid="{EB72EFF0-83A0-443B-9185-430E2226C809}"/>
+    <hyperlink ref="B4" r:id="rId5" xr:uid="{D1EB8FFB-0865-4CE2-BE87-112443020732}"/>
+    <hyperlink ref="B5" r:id="rId6" xr:uid="{15A92461-D135-45E8-9987-E8BE39328FE5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId7"/>
